--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>10</t>
+    <t>11</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>edcce0c</t>
+    <t>348580a</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 11:22:32 UTC</t>
+    <t>2026-06-23 12:05:24 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>11</t>
+    <t>12</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>348580a</t>
+    <t>cfbb4d3</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 12:05:24 UTC</t>
+    <t>2026-06-23 13:17:56 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>12</t>
+    <t>14</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>cfbb4d3</t>
+    <t>3eb8262</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 13:17:56 UTC</t>
+    <t>2026-06-23 13:38:42 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>14</t>
+    <t>15</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>3eb8262</t>
+    <t>0bdfd4b</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 13:38:42 UTC</t>
+    <t>2026-06-23 13:47:22 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>15</t>
+    <t>16</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>0bdfd4b</t>
+    <t>e40a5d4</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 13:47:22 UTC</t>
+    <t>2026-06-23 13:55:20 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>16</t>
+    <t>17</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>e40a5d4</t>
+    <t>d1d53d0</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 13:55:20 UTC</t>
+    <t>2026-06-23 14:03:15 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>17</t>
+    <t>18</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>d1d53d0</t>
+    <t>04fd2d2</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 14:03:15 UTC</t>
+    <t>2026-06-23 14:25:13 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>18</t>
+    <t>19</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>04fd2d2</t>
+    <t>af530d5</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 14:25:13 UTC</t>
+    <t>2026-06-23 14:35:05 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>19</t>
+    <t>20</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>af530d5</t>
+    <t>a38f0ce</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 14:35:05 UTC</t>
+    <t>2026-06-23 14:56:35 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>20</t>
+    <t>21</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>a38f0ce</t>
+    <t>6a5e7ca</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 14:56:35 UTC</t>
+    <t>2026-06-23 15:19:08 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>21</t>
+    <t>22</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>6a5e7ca</t>
+    <t>f8042b0</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 15:19:08 UTC</t>
+    <t>2026-06-23 15:33:18 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>22</t>
+    <t>23</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>f8042b0</t>
+    <t>19701a0</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 15:33:18 UTC</t>
+    <t>2026-06-23 15:40:10 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,7 +263,7 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>23</t>
+    <t>24</t>
   </si>
   <si>
     <t>Commit</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 15:40:10 UTC</t>
+    <t>2026-06-24 03:33:16 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>24</t>
+    <t>25</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>19701a0</t>
+    <t>f6dc91b</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-24 03:33:16 UTC</t>
+    <t>2026-06-24 04:39:37 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>25</t>
+    <t>26</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>f6dc91b</t>
+    <t>1b19601</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-24 04:39:37 UTC</t>
+    <t>2026-06-30 08:36:04 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>26</t>
+    <t>27</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>1b19601</t>
+    <t>9a48722</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 08:36:04 UTC</t>
+    <t>2026-06-30 13:20:16 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>27</t>
+    <t>28</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>9a48722</t>
+    <t>7bb6a7a</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 13:20:16 UTC</t>
+    <t>2026-06-30 13:28:29 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>28</t>
+    <t>29</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>7bb6a7a</t>
+    <t>c744b19</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 13:28:29 UTC</t>
+    <t>2026-06-30 13:37:17 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>29</t>
+    <t>30</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>c744b19</t>
+    <t>6c162b2</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 13:37:17 UTC</t>
+    <t>2026-06-30 13:45:12 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>30</t>
+    <t>31</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>6c162b2</t>
+    <t>4e802ad</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 13:45:12 UTC</t>
+    <t>2026-06-30 13:53:26 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>31</t>
+    <t>32</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>4e802ad</t>
+    <t>36ef16e</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 13:53:26 UTC</t>
+    <t>2026-06-30 14:16:06 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>32</t>
+    <t>34</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>36ef16e</t>
+    <t>16d388e</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 14:16:06 UTC</t>
+    <t>2026-06-30 14:27:04 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>34</t>
+    <t>36</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>16d388e</t>
+    <t>c0c6499</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 14:27:04 UTC</t>
+    <t>2026-06-30 14:33:44 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>36</t>
+    <t>37</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>c0c6499</t>
+    <t>69c8bfb</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 14:33:44 UTC</t>
+    <t>2026-06-30 14:41:30 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>37</t>
+    <t>38</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>69c8bfb</t>
+    <t>8620bea</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 14:41:30 UTC</t>
+    <t>2026-06-30 14:52:32 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>38</t>
+    <t>39</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>8620bea</t>
+    <t>bbf0a04</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 14:52:32 UTC</t>
+    <t>2026-06-30 15:10:53 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>39</t>
+    <t>41</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>bbf0a04</t>
+    <t>2e22a52</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 15:10:53 UTC</t>
+    <t>2026-06-30 15:18:21 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>41</t>
+    <t>42</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>2e22a52</t>
+    <t>bb12b5d</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 15:18:21 UTC</t>
+    <t>2026-06-30 17:18:18 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>42</t>
+    <t>43</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>bb12b5d</t>
+    <t>feb30ad</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 17:18:18 UTC</t>
+    <t>2026-06-30 17:33:50 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>43</t>
+    <t>44</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>feb30ad</t>
+    <t>dfc30c0</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 17:33:50 UTC</t>
+    <t>2026-06-30 17:45:39 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>45</t>
+    <t>46</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>6c3e421</t>
+    <t>f5c0ab7</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 04:27:16 UTC</t>
+    <t>2026-07-20 04:48:24 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>46</t>
+    <t>47</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>f5c0ab7</t>
+    <t>2dd4e06</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 04:48:24 UTC</t>
+    <t>2026-07-20 04:59:34 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>47</t>
+    <t>48</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>2dd4e06</t>
+    <t>a601b64</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 04:59:34 UTC</t>
+    <t>2026-07-20 05:11:11 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>48</t>
+    <t>49</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>a601b64</t>
+    <t>4642e1d</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 05:11:11 UTC</t>
+    <t>2026-07-20 05:17:43 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>49</t>
+    <t>50</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>4642e1d</t>
+    <t>6ff8f77</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 05:17:43 UTC</t>
+    <t>2026-07-20 05:23:58 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>50</t>
+    <t>51</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>6ff8f77</t>
+    <t>521b99b</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 05:23:58 UTC</t>
+    <t>2026-07-20 05:32:08 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>51</t>
+    <t>52</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>521b99b</t>
+    <t>44e8e58</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 05:32:08 UTC</t>
+    <t>2026-07-20 05:38:22 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>52</t>
+    <t>53</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>44e8e58</t>
+    <t>d05746b</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 05:38:22 UTC</t>
+    <t>2026-07-20 05:50:21 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>53</t>
+    <t>54</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>d05746b</t>
+    <t>c2b056c</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 05:50:21 UTC</t>
+    <t>2026-07-20 06:06:05 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>54</t>
+    <t>55</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>c2b056c</t>
+    <t>6166361</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 06:06:05 UTC</t>
+    <t>2026-07-20 06:13:32 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>55</t>
+    <t>56</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>6166361</t>
+    <t>ea04ba1</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 06:13:32 UTC</t>
+    <t>2026-07-20 11:13:09 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>56</t>
+    <t>57</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>ea04ba1</t>
+    <t>444b861</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 11:13:09 UTC</t>
+    <t>2026-07-20 11:26:52 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>57</t>
+    <t>58</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>444b861</t>
+    <t>2507a7b</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 11:26:52 UTC</t>
+    <t>2026-07-20 11:33:15 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>58</t>
+    <t>59</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>2507a7b</t>
+    <t>8511c2b</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 11:33:15 UTC</t>
+    <t>2026-07-20 15:14:04 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>59</t>
+    <t>60</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>8511c2b</t>
+    <t>0291447</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 15:14:04 UTC</t>
+    <t>2026-07-20 15:26:54 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>60</t>
+    <t>61</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>0291447</t>
+    <t>00ba088</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,13 +281,13 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 15:26:54 UTC</t>
+    <t>2026-07-21 10:04:59 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>
   </si>
   <si>
-    <t>4/100</t>
+    <t>15/100</t>
   </si>
   <si>
     <t>Critical Vulnerabilities</t>
@@ -1404,7 +1404,7 @@
         <v>95</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>61</t>
+    <t>62</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>00ba088</t>
+    <t>536fb94</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-21 10:04:59 UTC</t>
+    <t>2026-07-21 10:33:23 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>62</t>
+    <t>63</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>536fb94</t>
+    <t>9c8f524</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,13 +281,13 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-21 10:33:23 UTC</t>
+    <t>2026-07-21 10:56:35 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>
   </si>
   <si>
-    <t>15/100</t>
+    <t>10/100</t>
   </si>
   <si>
     <t>Critical Vulnerabilities</t>
@@ -1404,7 +1404,7 @@
         <v>95</v>
       </c>
       <c r="B10">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>63</t>
+    <t>64</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>9c8f524</t>
+    <t>ed920c1</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-21 10:56:35 UTC</t>
+    <t>2026-07-21 13:09:00 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>64</t>
+    <t>65</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>ed920c1</t>
+    <t>f0162ef</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-21 13:09:00 UTC</t>
+    <t>2026-07-21 13:43:21 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>65</t>
+    <t>66</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>f0162ef</t>
+    <t>c20f7b4</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-21 13:43:21 UTC</t>
+    <t>2026-07-21 13:54:08 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>66</t>
+    <t>67</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>c20f7b4</t>
+    <t>77d93ce</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-21 13:54:08 UTC</t>
+    <t>2026-07-21 14:13:41 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>67</t>
+    <t>68</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>77d93ce</t>
+    <t>14f8400</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-21 14:13:41 UTC</t>
+    <t>2026-07-21 14:23:02 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>68</t>
+    <t>69</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>14f8400</t>
+    <t>087f127</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-21 14:23:02 UTC</t>
+    <t>2026-07-21 14:37:42 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>69</t>
+    <t>70</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>087f127</t>
+    <t>6958884</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-21 14:37:42 UTC</t>
+    <t>2026-07-21 15:10:13 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>70</t>
+    <t>71</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>6958884</t>
+    <t>2d71144</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-21 15:10:13 UTC</t>
+    <t>2026-07-22 02:02:33 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>71</t>
+    <t>72</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>2d71144</t>
+    <t>a96e094</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-22 02:02:33 UTC</t>
+    <t>2026-07-22 02:47:33 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>72</t>
+    <t>73</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>a96e094</t>
+    <t>adc634e</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-22 02:47:33 UTC</t>
+    <t>2026-07-22 02:54:14 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>77</t>
+    <t>78</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>b0c83f8</t>
+    <t>6a5de8e</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-22 03:38:00 UTC</t>
+    <t>2026-07-22 03:44:31 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>80</t>
+    <t>81</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>e4fdde1</t>
+    <t>49466e1</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-22 04:12:10 UTC</t>
+    <t>2026-07-22 04:18:42 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -281,13 +281,13 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-22 04:18:42 UTC</t>
+    <t>2026-07-23 08:24:38 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>
   </si>
   <si>
-    <t>10/100</t>
+    <t>11/100</t>
   </si>
   <si>
     <t>Critical Vulnerabilities</t>
@@ -1404,7 +1404,7 @@
         <v>95</v>
       </c>
       <c r="B10">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -263,13 +263,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>81</t>
+    <t>82</t>
   </si>
   <si>
     <t>Commit</t>
   </si>
   <si>
-    <t>49466e1</t>
+    <t>c1ecc81</t>
   </si>
   <si>
     <t>Branch</t>
@@ -281,13 +281,13 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-23 08:24:38 UTC</t>
+    <t>2026-07-30 09:23:28 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>
   </si>
   <si>
-    <t>11/100</t>
+    <t>16/100</t>
   </si>
   <si>
     <t>Critical Vulnerabilities</t>
@@ -1404,7 +1404,7 @@
         <v>95</v>
       </c>
       <c r="B10">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -281,7 +281,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-30 09:23:28 UTC</t>
+    <t>2026-07-31 07:38:45 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>

--- a/reports/security/Security_Review_Report.xlsx
+++ b/reports/security/Security_Review_Report.xlsx
@@ -281,13 +281,13 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-31 07:38:45 UTC</t>
+    <t>2026-08-09 03:12:18 UTC</t>
   </si>
   <si>
     <t>Risk Score</t>
   </si>
   <si>
-    <t>16/100</t>
+    <t>29/100</t>
   </si>
   <si>
     <t>Critical Vulnerabilities</t>
@@ -1404,7 +1404,7 @@
         <v>95</v>
       </c>
       <c r="B10">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
